--- a/Daily_Purchase_list_details_October_2026.xlsx
+++ b/Daily_Purchase_list_details_October_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_October_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6B97A3B-A450-46EC-B481-3683459A3631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1288A925-E2AE-40E1-89D8-6BCFFF84166B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{4372692A-B248-4023-8853-7970FF453BFE}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="87">
   <si>
     <t>M/S KRISHI INFRATECH,SOMPETA</t>
   </si>
@@ -282,31 +282,37 @@
     <t>16-10-2026</t>
   </si>
   <si>
-    <t>Gireesh sir Food  Expensive</t>
-  </si>
-  <si>
     <t>259</t>
   </si>
   <si>
+    <t>261</t>
+  </si>
+  <si>
+    <t>Multi Meter Return Amount From FlipKart</t>
+  </si>
+  <si>
+    <t>Gunny bags, 40 Nos. (40 × 18) to store</t>
+  </si>
+  <si>
+    <t>Gunny bags, 100 Nos. (40 × 17) To Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TOTAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murali Technical works ,Printing papers for Crusher Weighmnet </t>
+  </si>
+  <si>
     <t>260</t>
   </si>
   <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>Multi Meter Return Amount From FlipKart</t>
-  </si>
-  <si>
-    <t>Gunny bags, 40 Nos. (40 × 18) to store</t>
-  </si>
-  <si>
-    <t>Gunny bags, 100 Nos. (40 × 17) To Store</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">        </t>
+    <t xml:space="preserve">VRL Logistics LTD Freight charges From Hyd to Palasa &amp;  Loading Charges </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murali Technical Works , Catridge Refilling for office </t>
   </si>
 </sst>
 </file>
@@ -398,7 +404,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -421,11 +427,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -506,6 +538,42 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1355,7 +1423,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DB2B1CF-979D-4909-98A4-84B992A64CC3}">
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
@@ -1425,7 +1493,7 @@
         <v>2181</v>
       </c>
       <c r="M4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1464,7 +1532,7 @@
       </c>
       <c r="F6" s="26"/>
       <c r="G6" s="26">
-        <f t="shared" ref="G6:G22" si="0">G5-E6+F6</f>
+        <f t="shared" ref="G6:G26" si="0">G5-E6+F6</f>
         <v>-3519</v>
       </c>
     </row>
@@ -1490,7 +1558,7 @@
         <v>-4019</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>47</v>
       </c>
@@ -1532,7 +1600,7 @@
         <v>-1619</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>53</v>
       </c>
@@ -1634,7 +1702,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
         <v>63</v>
       </c>
@@ -1705,7 +1773,7 @@
       </c>
       <c r="C18" s="25"/>
       <c r="D18" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E18" s="26">
         <v>720</v>
@@ -1760,14 +1828,14 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B21" s="25" t="s">
         <v>71</v>
       </c>
       <c r="C21" s="25"/>
       <c r="D21" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E21" s="26"/>
       <c r="F21" s="26">
@@ -1780,201 +1848,266 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="19"/>
+        <v>75</v>
+      </c>
+      <c r="C22" s="1"/>
       <c r="D22" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="26">
-        <v>1130</v>
+        <v>80</v>
+      </c>
+      <c r="E22" s="19">
+        <f>100*17</f>
+        <v>1700</v>
       </c>
       <c r="F22" s="19"/>
       <c r="G22" s="26">
         <f t="shared" si="0"/>
-        <v>5971</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="25" t="s">
+        <v>5401</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="1"/>
+      <c r="C23" s="38">
+        <v>2868125075</v>
+      </c>
       <c r="D23" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="19">
-        <f>100*17</f>
-        <v>1700</v>
+        <v>85</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1660</v>
       </c>
       <c r="F23" s="19"/>
       <c r="G23" s="26">
-        <f>G22-E23+F23</f>
-        <v>4271</v>
+        <f t="shared" si="0"/>
+        <v>3741</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
+      <c r="A24" s="25">
+        <v>262</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="19">
+        <v>505</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="7">
+        <v>250</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="26">
-        <f>G23-E24+F24</f>
-        <v>4271</v>
+        <f t="shared" si="0"/>
+        <v>3491</v>
       </c>
       <c r="I24" s="27"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
+      <c r="A25" s="25"/>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
-      <c r="D25" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="E25" s="17">
-        <f>SUM(E5:E23)</f>
-        <v>23250</v>
-      </c>
-      <c r="F25" s="17">
-        <f>SUM(F4:F23)</f>
-        <v>27521</v>
-      </c>
-      <c r="G25" s="16">
-        <f>G24-E24+F24</f>
-        <v>4271</v>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="26">
+        <f t="shared" si="0"/>
+        <v>3491</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
+      <c r="A26" s="25"/>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="26"/>
+      <c r="G26" s="26">
+        <f t="shared" si="0"/>
+        <v>3491</v>
+      </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="26">
+        <f>G26-E27+F27</f>
+        <v>3491</v>
+      </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="22" t="s">
+      <c r="A28" s="25"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E28" s="17">
+        <f>SUM(E5:E22)</f>
+        <v>22120</v>
+      </c>
+      <c r="F28" s="17">
+        <f>SUM(F4:F23)</f>
+        <v>27521</v>
+      </c>
+      <c r="G28" s="26">
+        <f>G27-E27+F27</f>
+        <v>3491</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="39"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="42"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="35"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="36"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="30"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="23"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="33"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="19"/>
+      <c r="A32" s="25"/>
       <c r="B32" s="19"/>
       <c r="C32" s="19"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="11"/>
+      <c r="D32" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="26"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="11"/>
+      <c r="A33" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="11"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="5"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15" t="s">
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="23"/>
+    </row>
+    <row r="35" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="19">
+        <v>262</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="19">
+        <v>505</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" s="19">
+        <v>2790</v>
+      </c>
+      <c r="F35" s="19"/>
+      <c r="G35" s="11"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="11"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="11"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="E35" s="16">
-        <f>SUM(E32:E34)</f>
+      <c r="E38" s="16">
+        <f>SUM(E35:E37)</f>
+        <v>2790</v>
+      </c>
+      <c r="F38" s="16"/>
+      <c r="G38" s="17">
+        <f>G37-E37+F37</f>
         <v>0</v>
       </c>
-      <c r="F35" s="16"/>
-      <c r="G35" s="17">
-        <f>G34-E34+F34</f>
-        <v>0</v>
-      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:G3" xr:uid="{6DB2B1CF-979D-4909-98A4-84B992A64CC3}"/>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="E29:G29"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Daily_Purchase_list_details_October_2026.xlsx
+++ b/Daily_Purchase_list_details_October_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_October_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1288A925-E2AE-40E1-89D8-6BCFFF84166B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EC7D11-9C31-46EC-83E2-CF96B5B01822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{4372692A-B248-4023-8853-7970FF453BFE}"/>
   </bookViews>
@@ -457,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -534,12 +534,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -550,15 +544,11 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -574,6 +564,12 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -905,22 +901,22 @@
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
@@ -1294,15 +1290,15 @@
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="29"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
       <c r="D26" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
@@ -1438,22 +1434,22 @@
     <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="28" t="s">
+      <c r="C1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
@@ -1874,7 +1870,7 @@
       <c r="B23" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="38">
+      <c r="C23" s="34">
         <v>2868125075</v>
       </c>
       <c r="D23" s="6" t="s">
@@ -1956,8 +1952,8 @@
         <v>81</v>
       </c>
       <c r="E28" s="17">
-        <f>SUM(E5:E22)</f>
-        <v>22120</v>
+        <f>SUM(E5:E26)</f>
+        <v>24030</v>
       </c>
       <c r="F28" s="17">
         <f>SUM(F4:F23)</f>
@@ -1969,33 +1965,30 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="39"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="42"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="36"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="38"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="35"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="37"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="36"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="G30" s="33"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="43" t="s">
+      <c r="A31" s="28"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="33"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="31"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="25"/>

--- a/Daily_Purchase_list_details_October_2026.xlsx
+++ b/Daily_Purchase_list_details_October_2026.xlsx
@@ -8,17 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_October_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EC7D11-9C31-46EC-83E2-CF96B5B01822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE40EE2-42F8-4543-A2BD-2AD32931843F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{4372692A-B248-4023-8853-7970FF453BFE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{4372692A-B248-4023-8853-7970FF453BFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Date_03-10-2026 to 09-10-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Date_10-10-2026 to 16-10-2026" sheetId="2" r:id="rId2"/>
+    <sheet name="Date_17-10-26 to 23-10-2026" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Date_03-10-2026 to 09-10-2026'!$A$3:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Date_10-10-2026 to 16-10-2026'!$A$3:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Date_17-10-26 to 23-10-2026'!$A$3:$G$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="121">
   <si>
     <t>M/S KRISHI INFRATECH,SOMPETA</t>
   </si>
@@ -313,6 +315,108 @@
   </si>
   <si>
     <t xml:space="preserve">Murali Technical Works , Catridge Refilling for office </t>
+  </si>
+  <si>
+    <t>265</t>
+  </si>
+  <si>
+    <t>17-10-26</t>
+  </si>
+  <si>
+    <t>{Amazon} Measuring Jug 1000ml for store. one No's</t>
+  </si>
+  <si>
+    <t>266</t>
+  </si>
+  <si>
+    <t>18-10-26</t>
+  </si>
+  <si>
+    <t>Disti Bommalu Big size 2 No's for Camp office.</t>
+  </si>
+  <si>
+    <t>267</t>
+  </si>
+  <si>
+    <t>Disti Bommalu Big size 1 No's for crusher</t>
+  </si>
+  <si>
+    <t>268</t>
+  </si>
+  <si>
+    <t>396102</t>
+  </si>
+  <si>
+    <t>Colin Glass Cleaner 1 lt pouch for office</t>
+  </si>
+  <si>
+    <t>269</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>270</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>Watchman torch light (Aluminum light)</t>
+  </si>
+  <si>
+    <t>271</t>
+  </si>
+  <si>
+    <t>Received money from Rajashekar through ph-pay</t>
+  </si>
+  <si>
+    <t>272</t>
+  </si>
+  <si>
+    <t>273</t>
+  </si>
+  <si>
+    <t>19-10-26</t>
+  </si>
+  <si>
+    <t>LBAAAF 9270152917</t>
+  </si>
+  <si>
+    <t>HP mouse wired one No's for Lab</t>
+  </si>
+  <si>
+    <t>274</t>
+  </si>
+  <si>
+    <t>22-10-26</t>
+  </si>
+  <si>
+    <t>paid to lineman shiva (Dasara Mamulu)</t>
+  </si>
+  <si>
+    <t>275</t>
+  </si>
+  <si>
+    <t>276</t>
+  </si>
+  <si>
+    <t>23-10-26</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>Tirupathi Electricals 3/4" cpvc pipe &amp; L-Bo &amp; tee bend &amp; Gatewall cpvc gum 250 ml Earth pipe for LC-352</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Steel plates for mess 15 No's x 200</t>
+  </si>
+  <si>
+    <t>277</t>
   </si>
 </sst>
 </file>
@@ -1414,6 +1518,7 @@
     <mergeCell ref="E26:G26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2104,5 +2209,545 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E63A5BEB-1971-4CF5-9919-1591BDBFA25A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="93.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
+        <v>3491</v>
+      </c>
+      <c r="G4" s="4">
+        <v>3491</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="19">
+        <v>169</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19">
+        <f>G4-E5+F5</f>
+        <v>3322</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="19">
+        <v>360</v>
+      </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19">
+        <f t="shared" ref="G6:G19" si="0">G5-E6+F6</f>
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19">
+        <f t="shared" si="0"/>
+        <v>2962</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="19">
+        <v>229</v>
+      </c>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19">
+        <f t="shared" si="0"/>
+        <v>2733</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="19">
+        <v>3000</v>
+      </c>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19">
+        <f t="shared" si="0"/>
+        <v>-267</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="19">
+        <v>350</v>
+      </c>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19">
+        <f t="shared" si="0"/>
+        <v>-617</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19">
+        <v>1000</v>
+      </c>
+      <c r="G11" s="19">
+        <f t="shared" si="0"/>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19">
+        <v>2000</v>
+      </c>
+      <c r="G12" s="19">
+        <f t="shared" si="0"/>
+        <v>2383</v>
+      </c>
+      <c r="M12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="19">
+        <v>265</v>
+      </c>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19">
+        <f t="shared" si="0"/>
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="19">
+        <v>2000</v>
+      </c>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19">
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19">
+        <v>2000</v>
+      </c>
+      <c r="G15" s="19">
+        <f t="shared" si="0"/>
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="19">
+        <v>1790</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19">
+        <f t="shared" si="0"/>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19">
+        <v>7000</v>
+      </c>
+      <c r="G17" s="19">
+        <f t="shared" si="0"/>
+        <v>7328</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="25"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19">
+        <f t="shared" si="0"/>
+        <v>7328</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="25"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19">
+        <f t="shared" si="0"/>
+        <v>7328</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="25"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="17">
+        <f>SUM(E5:E18)</f>
+        <v>8163</v>
+      </c>
+      <c r="F20" s="17">
+        <f>SUM(F4:F16)</f>
+        <v>8491</v>
+      </c>
+      <c r="G20" s="26">
+        <f>G19-E19+F19</f>
+        <v>7328</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="35"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="38"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="32"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="G22" s="33"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="31"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="25"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="26"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="23">
+        <v>7328</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>278</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="1">
+        <v>180</v>
+      </c>
+      <c r="F27" s="19"/>
+      <c r="G27" s="11">
+        <f>G26-E27+F27</f>
+        <v>7148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="11">
+        <f t="shared" ref="G28:G29" si="1">G27-E28+F28</f>
+        <v>7148</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="11">
+        <f t="shared" si="1"/>
+        <v>7148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="14"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="16">
+        <f>SUM(E27:E29)</f>
+        <v>180</v>
+      </c>
+      <c r="F30" s="16"/>
+      <c r="G30" s="17">
+        <f>G29-E29+F29</f>
+        <v>7148</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:G3" xr:uid="{E63A5BEB-1971-4CF5-9919-1591BDBFA25A}"/>
+  <mergeCells count="2">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToWidth="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Daily_Purchase_list_details_October_2026.xlsx
+++ b/Daily_Purchase_list_details_October_2026.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_October_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE40EE2-42F8-4543-A2BD-2AD32931843F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E048B436-A1F2-4545-B332-F6EFDB626AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="2" xr2:uid="{4372692A-B248-4023-8853-7970FF453BFE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" tabRatio="702" activeTab="3" xr2:uid="{4372692A-B248-4023-8853-7970FF453BFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Date_03-10-2026 to 09-10-2026" sheetId="1" r:id="rId1"/>
     <sheet name="Date_10-10-2026 to 16-10-2026" sheetId="2" r:id="rId2"/>
     <sheet name="Date_17-10-26 to 23-10-2026" sheetId="3" r:id="rId3"/>
+    <sheet name="Date_24-10-2026 to 30 -10-2026" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Date_03-10-2026 to 09-10-2026'!$A$3:$G$3</definedName>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="132">
   <si>
     <t>M/S KRISHI INFRATECH,SOMPETA</t>
   </si>
@@ -417,6 +418,39 @@
   </si>
   <si>
     <t>277</t>
+  </si>
+  <si>
+    <t>24-10-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 feet cement Rings 4 No's 4*320 &amp;  one cap 1*400  for LC-352 </t>
+  </si>
+  <si>
+    <t>LC-352 Electrical Bill  for  October Month</t>
+  </si>
+  <si>
+    <t>Pytm-929726031654</t>
+  </si>
+  <si>
+    <t>50mm Door  Locks   3 No's  For LC -352  Container</t>
+  </si>
+  <si>
+    <t>25-10-2026</t>
+  </si>
+  <si>
+    <t>Letters Tronsport charges from sompeta to Vizag</t>
+  </si>
+  <si>
+    <t>29-10-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LR_SOM595-AZ89955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sindhu Transport From Hyd to sompeta for Barbending Machine ,Cutting Machine ,Vibrator </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Received money from Rajashekar Through Cash </t>
   </si>
 </sst>
 </file>
@@ -2221,7 +2255,7 @@
   <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="93.85546875" bestFit="1" customWidth="1"/>
@@ -2289,7 +2323,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="19" t="s">
         <v>87</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -2309,7 +2343,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="19" t="s">
         <v>90</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -2329,7 +2363,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="19" t="s">
         <v>93</v>
       </c>
       <c r="B7" s="1"/>
@@ -2343,7 +2377,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="19" t="s">
         <v>95</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -2365,7 +2399,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="19" t="s">
         <v>98</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -2387,7 +2421,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="19" t="s">
         <v>100</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -2409,7 +2443,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="19" t="s">
         <v>103</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -2429,7 +2463,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="19" t="s">
         <v>105</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -2452,7 +2486,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="19" t="s">
         <v>106</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -2474,7 +2508,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="19" t="s">
         <v>110</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -2494,7 +2528,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="19" t="s">
         <v>113</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -2514,7 +2548,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="19" t="s">
         <v>114</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -2536,7 +2570,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="19" t="s">
         <v>120</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -2671,7 +2705,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="A27" s="19">
         <v>278</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -2750,4 +2784,387 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToWidth="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC92A6A2-2508-4007-B952-3FDD04C5F161}">
+  <dimension ref="A2:G26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="4" max="4" width="93.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="40" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4">
+        <v>6968</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
+        <v>278</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E6" s="19">
+        <v>1680</v>
+      </c>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19">
+        <f>G5-E6+F6</f>
+        <v>5288</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
+        <v>279</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="19">
+        <v>2543</v>
+      </c>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19">
+        <f t="shared" ref="G7:G15" si="0">G6-E7+F7</f>
+        <v>2745</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
+        <v>280</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="7">
+        <v>83</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="19">
+        <v>300</v>
+      </c>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19">
+        <f t="shared" si="0"/>
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
+        <v>281</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="19">
+        <v>200</v>
+      </c>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19">
+        <f t="shared" si="0"/>
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
+        <v>282</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="19">
+        <v>7820</v>
+      </c>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19">
+        <f t="shared" si="0"/>
+        <v>-5575</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
+        <v>283</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="34"/>
+      <c r="D11" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19">
+        <v>7000</v>
+      </c>
+      <c r="G11" s="19">
+        <f t="shared" si="0"/>
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="19"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19">
+        <f t="shared" si="0"/>
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="25"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19">
+        <f t="shared" si="0"/>
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="25"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19">
+        <f t="shared" si="0"/>
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="25"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="17">
+        <f>SUM(E6:E13)</f>
+        <v>12543</v>
+      </c>
+      <c r="F15" s="17">
+        <f>SUM(F5:F12)</f>
+        <v>7000</v>
+      </c>
+      <c r="G15" s="19">
+        <f>G14-E14+F14</f>
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="35"/>
+      <c r="B16" s="36"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="38"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="32"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="G17" s="33"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="28"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="31"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="25"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="26"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="23"/>
+      <c r="B21" s="23"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="23">
+        <v>7328</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="19"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="11"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="16">
+        <f>SUM(E22:E24)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="16"/>
+      <c r="G25" s="17">
+        <f>G24-E24+F24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>